--- a/evac_by_zip/evac_by_zip_2026-09-14.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-09-14.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -136,15 +136,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -555,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -781,209 +772,61 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Placed on a ZIP code (table above)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>225</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Not placed on any ZIP code (unmatched)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Reconciled total (matches morning report)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>362</v>
+      </c>
+      <c r="C11" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Placed on a ZIP code (table above)</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>330</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Not placed on any ZIP code (unmatched)</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>137</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Reconciled total (matches morning report)</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>467</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="D15" s="18" t="n">
+      <c r="D11" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="18" t="n">
-        <v>544</v>
+      <c r="E11" s="15" t="n">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1014,961 +857,506 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Evac Zone × ZIP Code Detail — 2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Zone Name</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Fire Name</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Evac Level</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>% of Zone</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>Est. Addresses</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>US-OR-UNI-UCO-140618N</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="G3" s="21" t="n">
+      <c r="G3" s="18" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>97021</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>NF 27</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="18" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>97023</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Clackamas</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>97886</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>US-OR-UNI-UCO-140618N</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>97063</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>NF 27</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>97358</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Clackamas</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Elk Mountain</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="20" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Mill Creek Buttes</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="20" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Cooper Spur North</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="22" t="n">
         <v>158</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Cooper Spur South</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="22" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Gibson Prairie</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>White River</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-043-L</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-043-N</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="n">
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1347-C</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G22" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1247</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="G24" s="25" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="G25" s="25" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1247</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G26" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G27" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G28" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -1976,8 +1364,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
